--- a/Data/National Accounts/PSA-14TAS_2018PSNA_Ann.xlsx
+++ b/Data/National Accounts/PSA-14TAS_2018PSNA_Ann.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Annl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Annl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CDF5818-7369-44A8-BD5A-9F647362E07E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B62EB223-1B6C-4399-AD26-BBC2FF3B996D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TAS" sheetId="1" r:id="rId1"/>
@@ -621,9 +621,6 @@
     <t>2023 - 2024</t>
   </si>
   <si>
-    <t>As of January 2026</t>
-  </si>
-  <si>
     <t>Annual 2000 to 2025</t>
   </si>
   <si>
@@ -631,6 +628,9 @@
   </si>
   <si>
     <t>2024 - 2025</t>
+  </si>
+  <si>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -23592,7 +23592,7 @@
     </row>
     <row r="3" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:96" x14ac:dyDescent="0.2">
@@ -23602,7 +23602,7 @@
     </row>
     <row r="6" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -23885,10 +23885,10 @@
         <v>530701.62661504303</v>
       </c>
       <c r="Z12" s="9">
-        <v>577446.77103678649</v>
+        <v>577172.00200369989</v>
       </c>
       <c r="AA12" s="9">
-        <v>614189.37865707395</v>
+        <v>613389.00287143979</v>
       </c>
       <c r="AB12" s="10"/>
       <c r="AC12" s="10"/>
@@ -24037,10 +24037,10 @@
         <v>40502.051408822132</v>
       </c>
       <c r="Z13" s="9">
-        <v>50132.193637816912</v>
+        <v>50066.478823148551</v>
       </c>
       <c r="AA13" s="9">
-        <v>56415.241822850941</v>
+        <v>56817.840331578729</v>
       </c>
       <c r="AB13" s="10"/>
       <c r="AC13" s="10"/>
@@ -24192,7 +24192,7 @@
         <v>159500.48500677687</v>
       </c>
       <c r="AA14" s="9">
-        <v>167239.83067685564</v>
+        <v>167138.41676220563</v>
       </c>
       <c r="AB14" s="10"/>
       <c r="AC14" s="10"/>
@@ -24341,10 +24341,10 @@
         <v>231644.56470357621</v>
       </c>
       <c r="Z15" s="9">
-        <v>249780.20391925785</v>
+        <v>249422.02915419944</v>
       </c>
       <c r="AA15" s="9">
-        <v>275365.07308501564</v>
+        <v>273354.89228291612</v>
       </c>
       <c r="AB15" s="10"/>
       <c r="AC15" s="10"/>
@@ -24496,7 +24496,7 @@
         <v>38671.480368313896</v>
       </c>
       <c r="AA16" s="9">
-        <v>45528.77039692059</v>
+        <v>45529.629730551911</v>
       </c>
       <c r="AB16" s="10"/>
       <c r="AC16" s="10"/>
@@ -24743,10 +24743,10 @@
         <v>977711.79854265321</v>
       </c>
       <c r="Z18" s="12">
-        <v>1075531.1339689521</v>
+        <v>1074832.4753561385</v>
       </c>
       <c r="AA18" s="12">
-        <v>1158738.2946387168</v>
+        <v>1156229.7819786924</v>
       </c>
       <c r="AB18" s="10"/>
       <c r="AC18" s="10"/>
@@ -25060,7 +25060,7 @@
     </row>
     <row r="25" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:96" ht="15" x14ac:dyDescent="0.2">
@@ -25125,7 +25125,7 @@
     </row>
     <row r="28" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -25408,10 +25408,10 @@
         <v>393331.53497880761</v>
       </c>
       <c r="Z34" s="9">
-        <v>422082.29376348818</v>
+        <v>421865.26809788909</v>
       </c>
       <c r="AA34" s="9">
-        <v>444631.92629562179</v>
+        <v>443974.54206267465</v>
       </c>
       <c r="AB34" s="10"/>
       <c r="AC34" s="10"/>
@@ -25560,10 +25560,10 @@
         <v>36466.980809222077</v>
       </c>
       <c r="Z35" s="9">
-        <v>44122.212732615284</v>
+        <v>44066.215728728806</v>
       </c>
       <c r="AA35" s="9">
-        <v>48220.24641187246</v>
+        <v>48563.968245782693</v>
       </c>
       <c r="AB35" s="10"/>
       <c r="AC35" s="10"/>
@@ -25715,7 +25715,7 @@
         <v>123908.32664744252</v>
       </c>
       <c r="AA36" s="9">
-        <v>130445.83522486252</v>
+        <v>130273.9309824729</v>
       </c>
       <c r="AB36" s="10"/>
       <c r="AC36" s="10"/>
@@ -25864,10 +25864,10 @@
         <v>196372.84516749156</v>
       </c>
       <c r="Z37" s="9">
-        <v>208435.21785500966</v>
+        <v>208138.42593700122</v>
       </c>
       <c r="AA37" s="9">
-        <v>225794.04193653073</v>
+        <v>224160.01479894697</v>
       </c>
       <c r="AB37" s="10"/>
       <c r="AC37" s="10"/>
@@ -26019,7 +26019,7 @@
         <v>37343.319950227407</v>
       </c>
       <c r="AA38" s="9">
-        <v>43947.135001764364</v>
+        <v>43948.548751430164</v>
       </c>
       <c r="AB38" s="10"/>
       <c r="AC38" s="10"/>
@@ -26266,10 +26266,10 @@
         <v>767806.39153391449</v>
       </c>
       <c r="Z40" s="12">
-        <v>835891.37094878312</v>
+        <v>835321.556361289</v>
       </c>
       <c r="AA40" s="12">
-        <v>893039.18487065192</v>
+        <v>890921.00484130741</v>
       </c>
       <c r="AB40" s="10"/>
       <c r="AC40" s="10"/>
@@ -26583,7 +26583,7 @@
     </row>
     <row r="47" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49" spans="1:91" x14ac:dyDescent="0.2">
@@ -26593,7 +26593,7 @@
     </row>
     <row r="50" spans="1:91" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51" spans="1:91" x14ac:dyDescent="0.2">
@@ -26712,7 +26712,7 @@
         <v>49</v>
       </c>
       <c r="Z54" s="18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AA54" s="18"/>
     </row>
@@ -26793,10 +26793,10 @@
         <v>21.297555038839434</v>
       </c>
       <c r="Y56" s="19">
-        <v>8.8081780943270331</v>
+        <v>8.7564034210818846</v>
       </c>
       <c r="Z56" s="19">
-        <v>6.3629427790058202</v>
+        <v>6.2749060491516673</v>
       </c>
       <c r="AA56" s="19"/>
       <c r="AB56" s="10"/>
@@ -26938,10 +26938,10 @@
         <v>19.720825453205748</v>
       </c>
       <c r="Y57" s="19">
-        <v>23.776924610038748</v>
+        <v>23.61467402671633</v>
       </c>
       <c r="Z57" s="19">
-        <v>12.532960816409286</v>
+        <v>13.484793952213465</v>
       </c>
       <c r="AA57" s="19"/>
       <c r="AB57" s="10"/>
@@ -27086,7 +27086,7 @@
         <v>14.855860984686316</v>
       </c>
       <c r="Z58" s="19">
-        <v>4.8522395839422927</v>
+        <v>4.7886573856526127</v>
       </c>
       <c r="AA58" s="19"/>
       <c r="AB58" s="10"/>
@@ -27228,10 +27228,10 @@
         <v>9.7583466577479072</v>
       </c>
       <c r="Y59" s="19">
-        <v>7.8290804012124795</v>
+        <v>7.6744578373216541</v>
       </c>
       <c r="Z59" s="19">
-        <v>10.242953110098412</v>
+        <v>9.5953285320763371</v>
       </c>
       <c r="AA59" s="19"/>
       <c r="AB59" s="10"/>
@@ -27376,7 +27376,7 @@
         <v>7.4404031776320352</v>
       </c>
       <c r="Z60" s="19">
-        <v>17.732163246135585</v>
+        <v>17.734385384060317</v>
       </c>
       <c r="AA60" s="19"/>
       <c r="AB60" s="10"/>
@@ -27611,10 +27611,10 @@
         <v>21.105370715867224</v>
       </c>
       <c r="Y62" s="19">
-        <v>10.004925334040692</v>
+        <v>9.9334667903415266</v>
       </c>
       <c r="Z62" s="19">
-        <v>7.7363786172057729</v>
+        <v>7.5730226327208214</v>
       </c>
       <c r="AA62" s="19"/>
       <c r="AB62" s="10"/>
@@ -27914,7 +27914,7 @@
     </row>
     <row r="69" spans="1:91" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="71" spans="1:91" x14ac:dyDescent="0.2">
@@ -27924,7 +27924,7 @@
     </row>
     <row r="72" spans="1:91" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="73" spans="1:91" x14ac:dyDescent="0.2">
@@ -28040,7 +28040,7 @@
         <v>49</v>
       </c>
       <c r="Z76" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AA76" s="7"/>
     </row>
@@ -28121,10 +28121,10 @@
         <v>12.862538088995535</v>
       </c>
       <c r="Y78" s="19">
-        <v>7.3095483651545123</v>
+        <v>7.2543720962060263</v>
       </c>
       <c r="Z78" s="19">
-        <v>5.3424729881631094</v>
+        <v>5.2408376884098828</v>
       </c>
       <c r="AA78" s="19"/>
       <c r="AB78" s="10"/>
@@ -28266,10 +28266,10 @@
         <v>16.810494970778066</v>
       </c>
       <c r="Y79" s="19">
-        <v>20.992228458510851</v>
+        <v>20.838673097897285</v>
       </c>
       <c r="Z79" s="19">
-        <v>9.2879151462589675</v>
+        <v>10.206804561440009</v>
       </c>
       <c r="AA79" s="19"/>
       <c r="AB79" s="10"/>
@@ -28414,7 +28414,7 @@
         <v>16.257727071174301</v>
       </c>
       <c r="Z80" s="19">
-        <v>5.2760849527257534</v>
+        <v>5.1373499322143914</v>
       </c>
       <c r="AA80" s="19"/>
       <c r="AB80" s="10"/>
@@ -28556,10 +28556,10 @@
         <v>3.8532363038192159</v>
       </c>
       <c r="Y81" s="19">
-        <v>6.1425869127830595</v>
+        <v>5.9914499682858207</v>
       </c>
       <c r="Z81" s="19">
-        <v>8.3281627069356858</v>
+        <v>7.6975641522316209</v>
       </c>
       <c r="AA81" s="19"/>
       <c r="AB81" s="10"/>
@@ -28704,7 +28704,7 @@
         <v>6.5299048022272785</v>
       </c>
       <c r="Z82" s="19">
-        <v>17.684059854182138</v>
+        <v>17.687845670943176</v>
       </c>
       <c r="AA82" s="19"/>
       <c r="AB82" s="10"/>
@@ -28939,10 +28939,10 @@
         <v>13.017170638964501</v>
       </c>
       <c r="Y84" s="19">
-        <v>8.8674671330684305</v>
+        <v>8.7932538165635066</v>
       </c>
       <c r="Z84" s="19">
-        <v>6.8367512703239015</v>
+        <v>6.6560533553345493</v>
       </c>
       <c r="AA84" s="19"/>
       <c r="AB84" s="10"/>
@@ -29238,7 +29238,7 @@
     </row>
     <row r="90" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="92" spans="1:92" x14ac:dyDescent="0.2">
@@ -29248,7 +29248,7 @@
     </row>
     <row r="93" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="94" spans="1:92" x14ac:dyDescent="0.2">
@@ -29450,10 +29450,10 @@
         <v>134.9247592475993</v>
       </c>
       <c r="Z99" s="19">
-        <v>136.80904874923658</v>
+        <v>136.81429727696229</v>
       </c>
       <c r="AA99" s="19">
-        <v>138.13434041367483</v>
+        <v>138.15859801818306</v>
       </c>
       <c r="AB99" s="10"/>
       <c r="AC99" s="10"/>
@@ -29602,10 +29602,10 @@
         <v>111.06499773235856</v>
       </c>
       <c r="Z100" s="19">
-        <v>113.62121374470195</v>
+        <v>113.61647011251728</v>
       </c>
       <c r="AA100" s="19">
-        <v>116.99492644849026</v>
+        <v>116.99587653962524</v>
       </c>
       <c r="AB100" s="10"/>
       <c r="AC100" s="10"/>
@@ -29757,7 +29757,7 @@
         <v>128.72458964005304</v>
       </c>
       <c r="AA101" s="19">
-        <v>128.20633973370451</v>
+        <v>128.29766899771568</v>
       </c>
       <c r="AB101" s="10"/>
       <c r="AC101" s="10"/>
@@ -29906,10 +29906,10 @@
         <v>117.96160742387802</v>
       </c>
       <c r="Z102" s="19">
-        <v>119.83589265275138</v>
+        <v>119.83468599387497</v>
       </c>
       <c r="AA102" s="19">
-        <v>121.95409175695566</v>
+        <v>121.94632148293391</v>
       </c>
       <c r="AB102" s="10"/>
       <c r="AC102" s="10"/>
@@ -30061,7 +30061,7 @@
         <v>103.5566211570281</v>
       </c>
       <c r="AA103" s="19">
-        <v>103.59894995451404</v>
+        <v>103.59757267086162</v>
       </c>
       <c r="AB103" s="10"/>
       <c r="AC103" s="10"/>
@@ -30308,10 +30308,10 @@
         <v>127.33832504173247</v>
       </c>
       <c r="Z105" s="19">
-        <v>128.6687686162096</v>
+        <v>128.67290053403789</v>
       </c>
       <c r="AA105" s="19">
-        <v>129.75223419860896</v>
+        <v>129.77915838729635</v>
       </c>
       <c r="AB105" s="10"/>
       <c r="AC105" s="10"/>
@@ -30429,7 +30429,7 @@
     </row>
     <row r="112" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="114" spans="1:96" x14ac:dyDescent="0.2">
@@ -30439,7 +30439,7 @@
     </row>
     <row r="115" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="116" spans="1:96" x14ac:dyDescent="0.2">
@@ -30641,10 +30641,10 @@
         <v>54.279965466929049</v>
       </c>
       <c r="Z121" s="19">
-        <v>53.6894519181307</v>
+        <v>53.698787042367492</v>
       </c>
       <c r="AA121" s="19">
-        <v>53.005012563995059</v>
+        <v>53.050787346242537</v>
       </c>
       <c r="AB121" s="10"/>
       <c r="AC121" s="10"/>
@@ -30793,10 +30793,10 @@
         <v>4.1425347908446266</v>
       </c>
       <c r="Z122" s="19">
-        <v>4.661156897691825</v>
+        <v>4.6580727667871553</v>
       </c>
       <c r="AA122" s="19">
-        <v>4.8686784655236286</v>
+        <v>4.9140613065981205</v>
       </c>
       <c r="AB122" s="10"/>
       <c r="AC122" s="10"/>
@@ -30945,10 +30945,10 @@
         <v>14.203585509750335</v>
       </c>
       <c r="Z123" s="19">
-        <v>14.829927276785021</v>
+        <v>14.839566971022853</v>
       </c>
       <c r="AA123" s="19">
-        <v>14.432925143722755</v>
+        <v>14.455467188898766</v>
       </c>
       <c r="AB123" s="10"/>
       <c r="AC123" s="10"/>
@@ -31097,10 +31097,10 @@
         <v>23.692520132093975</v>
       </c>
       <c r="Z124" s="19">
-        <v>23.223893389074906</v>
+        <v>23.205665522113588</v>
       </c>
       <c r="AA124" s="19">
-        <v>23.764216161585626</v>
+        <v>23.641917596614341</v>
       </c>
       <c r="AB124" s="10"/>
       <c r="AC124" s="10"/>
@@ -31249,10 +31249,10 @@
         <v>3.6813941003820023</v>
       </c>
       <c r="Z125" s="19">
-        <v>3.5955705183175333</v>
+        <v>3.5979076977089255</v>
       </c>
       <c r="AA125" s="19">
-        <v>3.9291676651729208</v>
+        <v>3.9377665616462174</v>
       </c>
       <c r="AB125" s="10"/>
       <c r="AC125" s="10"/>
@@ -31816,7 +31816,7 @@
     </row>
     <row r="134" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="136" spans="1:96" x14ac:dyDescent="0.2">
@@ -31826,7 +31826,7 @@
     </row>
     <row r="137" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="138" spans="1:96" x14ac:dyDescent="0.2">
@@ -32028,10 +32028,10 @@
         <v>51.227957896132459</v>
       </c>
       <c r="Z143" s="19">
-        <v>50.494873907407531</v>
+        <v>50.503337892482932</v>
       </c>
       <c r="AA143" s="19">
-        <v>49.788624489083574</v>
+        <v>49.833210761683219</v>
       </c>
       <c r="AB143" s="10"/>
       <c r="AC143" s="10"/>
@@ -32180,10 +32180,10 @@
         <v>4.749502115548788</v>
       </c>
       <c r="Z144" s="19">
-        <v>5.2784625210969844</v>
+        <v>5.2753595777755207</v>
       </c>
       <c r="AA144" s="19">
-        <v>5.3995666963770121</v>
+        <v>5.4509847654150887</v>
       </c>
       <c r="AB144" s="10"/>
       <c r="AC144" s="10"/>
@@ -32332,10 +32332,10 @@
         <v>13.88119774517107</v>
       </c>
       <c r="Z145" s="19">
-        <v>14.823496324265159</v>
+        <v>14.833608172066654</v>
       </c>
       <c r="AA145" s="19">
-        <v>14.606955376068559</v>
+        <v>14.622388547868791</v>
       </c>
       <c r="AB145" s="10"/>
       <c r="AC145" s="10"/>
@@ -32484,10 +32484,10 @@
         <v>25.57582840319683</v>
       </c>
       <c r="Z146" s="19">
-        <v>24.935682446203998</v>
+        <v>24.917162061956681</v>
       </c>
       <c r="AA146" s="19">
-        <v>25.283777661921388</v>
+        <v>25.160481522026164</v>
       </c>
       <c r="AB146" s="10"/>
       <c r="AC146" s="10"/>
@@ -32636,10 +32636,10 @@
         <v>4.565513839950853</v>
       </c>
       <c r="Z147" s="19">
-        <v>4.467484801026318</v>
+        <v>4.4705322957182085</v>
       </c>
       <c r="AA147" s="19">
-        <v>4.9210757765494559</v>
+        <v>4.9329344030067359</v>
       </c>
       <c r="AB147" s="10"/>
       <c r="AC147" s="10"/>
